--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_PBDKS-CSTD-A0-01-C-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_PBDKS-CSTD-A0-01-C-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A42BA1D-C517-4C07-97F8-D3C7AB31402D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F82E77C-6243-43EF-BC92-485253E26786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14265" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="1005" windowWidth="22740" windowHeight="14070" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="310">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -3217,6 +3217,19 @@
   <si>
     <t>(株)デンソー</t>
   </si>
+  <si>
+    <t>RWの削除
+[Reference]シート
+RW記載を対象外に変更</t>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2.1.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -4641,7 +4654,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="302">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5395,16 +5408,37 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5449,31 +5483,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5526,6 +5539,15 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -11124,6 +11146,188 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D7085DF-8487-4B40-B6C6-0ED4617E7B25}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15865929" y="18777857"/>
+          <a:ext cx="830035" cy="3837214"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>85</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E37B324-5F8B-4C02-8365-A47DCFAFBB12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18788063" y="5334000"/>
+          <a:ext cx="44886562" cy="5167313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -27660,10 +27864,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="52" width="2.08984375" style="207" customWidth="1"/>
-    <col min="53" max="16384" width="8.08984375" style="207"/>
+    <col min="1" max="52" width="2.125" style="207" customWidth="1"/>
+    <col min="53" max="16384" width="8.125" style="207"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -28100,17 +28304,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <dimension ref="B2:X14"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="18" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" hidden="1" customWidth="1"/>
     <col min="19" max="22" width="0" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -28162,8 +28366,8 @@
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="23" t="str">
-        <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>2.0.2</v>
+        <f>DGET(B8:C15,"Ver.",H4:H5)</f>
+        <v>2.1.0</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -28176,11 +28380,11 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="H5" s="11">
-        <f>MAX(B9:B14)</f>
-        <v>4</v>
+        <f>MAX(B9:B15)</f>
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
       <c r="C7" s="245" t="s">
         <v>0</v>
@@ -28215,7 +28419,7 @@
       <c r="W7" s="243"/>
       <c r="X7" s="244"/>
     </row>
-    <row r="8" spans="2:24" ht="26.5" thickBot="1">
+    <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>93</v>
       </c>
@@ -28286,7 +28490,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="13.5" thickTop="1">
+    <row r="9" spans="2:24" ht="14.25" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -28338,9 +28542,9 @@
         <v>45301</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="91">
+    <row r="10" spans="2:24" ht="94.5">
       <c r="B10" s="9">
-        <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
+        <f t="shared" ref="B10:B14" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -28378,7 +28582,7 @@
         <v>45371</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="52">
+    <row r="11" spans="2:24" ht="54">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -28430,7 +28634,7 @@
         <v>45806</v>
       </c>
     </row>
-    <row r="12" spans="2:24" ht="117">
+    <row r="12" spans="2:24" ht="121.5">
       <c r="B12" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -28470,33 +28674,65 @@
         <v>46008</v>
       </c>
     </row>
-    <row r="13" spans="2:24" ht="13.5" thickBot="1">
+    <row r="13" spans="2:24" ht="40.5">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="196"/>
+        <v>5</v>
+      </c>
+      <c r="C13" s="232" t="s">
+        <v>309</v>
+      </c>
+      <c r="D13" s="233" t="s">
+        <v>308</v>
+      </c>
+      <c r="E13" s="234"/>
+      <c r="F13" s="234"/>
+      <c r="G13" s="299"/>
+      <c r="H13" s="299"/>
+      <c r="I13" s="299"/>
+      <c r="J13" s="299"/>
+      <c r="K13" s="299"/>
+      <c r="L13" s="299"/>
+      <c r="M13" s="299"/>
+      <c r="N13" s="299"/>
+      <c r="O13" s="299"/>
+      <c r="P13" s="299"/>
+      <c r="Q13" s="299"/>
+      <c r="R13" s="299"/>
+      <c r="S13" s="299"/>
+      <c r="T13" s="300"/>
+      <c r="U13" s="299"/>
+      <c r="V13" s="300"/>
+      <c r="W13" s="301"/>
+      <c r="X13" s="236"/>
+    </row>
+    <row r="14" spans="2:24" ht="14.25" thickBot="1">
+      <c r="B14" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="196"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -28521,11 +28757,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28539,13 +28775,13 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="151" t="s">
         <v>140</v>
       </c>
       <c r="C6" s="151"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="82" t="s">
         <v>142</v>
       </c>
@@ -28565,7 +28801,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="27">
       <c r="C9" s="160">
         <v>1</v>
       </c>
@@ -28576,7 +28812,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="158"/>
       <c r="D10" s="93"/>
       <c r="E10" s="5"/>
@@ -28584,14 +28820,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="156"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="151" t="s">
         <v>141</v>
       </c>
       <c r="C12" s="89"/>
       <c r="D12" s="89"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="152"/>
       <c r="C13" s="157" t="s">
         <v>142</v>
@@ -28603,7 +28839,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="154">
         <v>0</v>
       </c>
@@ -28680,17 +28916,17 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="158"/>
       <c r="D21" s="93"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="151" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="157" t="s">
         <v>142</v>
       </c>
@@ -28777,12 +29013,12 @@
       <c r="D33" s="92"/>
       <c r="E33" s="78"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="158"/>
       <c r="D34" s="93"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="151" t="s">
         <v>188</v>
       </c>
@@ -28794,7 +29030,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
       <c r="C39" s="253"/>
       <c r="D39" s="254"/>
       <c r="E39" s="5" t="s">
@@ -28822,133 +29058,133 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="255" t="s">
+      <c r="B2" s="280" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="256"/>
-      <c r="D2" s="261" t="s">
+      <c r="C2" s="281"/>
+      <c r="D2" s="268" t="s">
         <v>283</v>
       </c>
-      <c r="E2" s="262"/>
-      <c r="F2" s="262"/>
-      <c r="G2" s="262"/>
-      <c r="H2" s="263"/>
+      <c r="E2" s="269"/>
+      <c r="F2" s="269"/>
+      <c r="G2" s="269"/>
+      <c r="H2" s="270"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="257" t="s">
+      <c r="B3" s="255" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="258"/>
-      <c r="D3" s="264" t="s">
+      <c r="C3" s="256"/>
+      <c r="D3" s="271" t="s">
         <v>290</v>
       </c>
-      <c r="E3" s="265"/>
-      <c r="F3" s="265"/>
-      <c r="G3" s="265"/>
-      <c r="H3" s="266"/>
+      <c r="E3" s="272"/>
+      <c r="F3" s="272"/>
+      <c r="G3" s="272"/>
+      <c r="H3" s="273"/>
     </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="259" t="s">
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="266" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="260"/>
-      <c r="D4" s="267" t="str">
+      <c r="C4" s="267"/>
+      <c r="D4" s="274" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_PBDKS-CSTD-A0-01-C-C0.c</v>
       </c>
-      <c r="E4" s="268"/>
-      <c r="F4" s="268"/>
-      <c r="G4" s="268"/>
-      <c r="H4" s="269"/>
+      <c r="E4" s="275"/>
+      <c r="F4" s="275"/>
+      <c r="G4" s="275"/>
+      <c r="H4" s="276"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="255" t="s">
+      <c r="B6" s="280" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="256"/>
-      <c r="D6" s="270" t="str">
+      <c r="C6" s="281"/>
+      <c r="D6" s="277" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_PBDKS</v>
       </c>
-      <c r="E6" s="271"/>
-      <c r="F6" s="271"/>
-      <c r="G6" s="271"/>
-      <c r="H6" s="272"/>
+      <c r="E6" s="278"/>
+      <c r="F6" s="278"/>
+      <c r="G6" s="278"/>
+      <c r="H6" s="279"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="257" t="s">
+      <c r="B7" s="255" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="258"/>
-      <c r="D7" s="273">
+      <c r="C7" s="256"/>
+      <c r="D7" s="257">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="274"/>
-      <c r="F7" s="274"/>
-      <c r="G7" s="274"/>
-      <c r="H7" s="275"/>
+      <c r="E7" s="258"/>
+      <c r="F7" s="258"/>
+      <c r="G7" s="258"/>
+      <c r="H7" s="259"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="257" t="s">
+      <c r="B8" s="255" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="258"/>
-      <c r="D8" s="273" t="str">
+      <c r="C8" s="256"/>
+      <c r="D8" s="257" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_PBDKS_MTRX</v>
       </c>
-      <c r="E8" s="274"/>
-      <c r="F8" s="274"/>
-      <c r="G8" s="274"/>
-      <c r="H8" s="275"/>
+      <c r="E8" s="258"/>
+      <c r="F8" s="258"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="259"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="257" t="s">
+      <c r="B9" s="255" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="258"/>
-      <c r="D9" s="276" t="s">
+      <c r="C9" s="256"/>
+      <c r="D9" s="260" t="s">
         <v>236</v>
       </c>
-      <c r="E9" s="277"/>
-      <c r="F9" s="277"/>
-      <c r="G9" s="277"/>
-      <c r="H9" s="278"/>
+      <c r="E9" s="261"/>
+      <c r="F9" s="261"/>
+      <c r="G9" s="261"/>
+      <c r="H9" s="262"/>
     </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="259" t="s">
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="266" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="260"/>
-      <c r="D10" s="279" t="s">
+      <c r="C10" s="267"/>
+      <c r="D10" s="263" t="s">
         <v>237</v>
       </c>
-      <c r="E10" s="280"/>
-      <c r="F10" s="280"/>
-      <c r="G10" s="280"/>
-      <c r="H10" s="281"/>
+      <c r="E10" s="264"/>
+      <c r="F10" s="264"/>
+      <c r="G10" s="264"/>
+      <c r="H10" s="265"/>
     </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="142" t="s">
         <v>34</v>
       </c>
@@ -28983,7 +29219,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="111">
         <v>1</v>
       </c>
@@ -29836,7 +30072,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="102">
         <v>25</v>
       </c>
@@ -29877,22 +30113,22 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -29932,21 +30168,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>216</v>
       </c>
@@ -29954,7 +30190,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="142" t="s">
         <v>34</v>
       </c>
@@ -29986,7 +30222,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="173">
         <v>0</v>
       </c>
@@ -30008,7 +30244,7 @@
       </c>
       <c r="R4" s="141"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="176">
         <v>1</v>
       </c>
@@ -30536,7 +30772,7 @@
       <c r="Q28" s="146"/>
       <c r="R28" s="120"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="177">
         <v>25</v>
       </c>
@@ -30558,7 +30794,7 @@
       <c r="Q29" s="144"/>
       <c r="R29" s="122"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>217</v>
       </c>
@@ -30566,7 +30802,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="142" t="s">
         <v>34</v>
       </c>
@@ -30598,7 +30834,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="173">
         <v>0</v>
       </c>
@@ -30624,7 +30860,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="176">
         <v>1</v>
       </c>
@@ -31152,7 +31388,7 @@
       <c r="Q58" s="146"/>
       <c r="R58" s="178"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="177">
         <v>25</v>
       </c>
@@ -31200,29 +31436,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="95" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="103" t="s">
         <v>58</v>
       </c>
@@ -31266,7 +31502,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="25"/>
       <c r="C3" s="54" t="s">
         <v>110</v>
@@ -31287,7 +31523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="25" t="s">
         <v>238</v>
       </c>
@@ -31575,7 +31811,7 @@
       </c>
       <c r="U12" s="31"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="25"/>
       <c r="C13" s="24"/>
       <c r="D13" s="119"/>
@@ -33826,7 +34062,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="56"/>
       <c r="C103" s="57"/>
       <c r="D103" s="121"/>
@@ -33896,18 +34132,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -34131,7 +34367,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
       <c r="A4" s="286" t="s">
         <v>63</v>
       </c>
@@ -34179,7 +34415,7 @@
       <c r="AV4" s="85"/>
       <c r="AW4" s="86"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
       <c r="A5" s="288"/>
       <c r="B5" s="289"/>
       <c r="C5" s="138"/>
@@ -35696,7 +35932,7 @@
         <v>ALERT_VOM_BAT_WT</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="134"/>
       <c r="C17" s="50">
         <f t="shared" si="4"/>
@@ -42076,7 +42312,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="59" t="s">
         <v>64</v>
       </c>
@@ -62699,16 +62935,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B3:AY178"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="42.6328125" customWidth="1"/>
-    <col min="13" max="13" width="20.90625" customWidth="1"/>
-    <col min="14" max="14" width="10.90625" customWidth="1"/>
-    <col min="15" max="15" width="34.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="10.90625" customWidth="1"/>
+    <col min="12" max="12" width="42.625" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="10.875" customWidth="1"/>
+    <col min="15" max="15" width="34.375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="21:51">
@@ -62781,18 +63017,18 @@
       <c r="AX92" s="197"/>
       <c r="AY92" s="197"/>
     </row>
-    <row r="101" spans="2:51" ht="14">
+    <row r="101" spans="2:51" ht="14.25">
       <c r="B101" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="102" spans="2:51" ht="14">
+    <row r="102" spans="2:51" ht="14.25">
       <c r="B102" s="26"/>
     </row>
-    <row r="103" spans="2:51" ht="14.5" thickBot="1">
+    <row r="103" spans="2:51" ht="15" thickBot="1">
       <c r="B103" s="26"/>
     </row>
-    <row r="104" spans="2:51" ht="14.5" thickBot="1">
+    <row r="104" spans="2:51" ht="15" thickBot="1">
       <c r="B104" s="100" t="s">
         <v>170</v>
       </c>
@@ -62949,7 +63185,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="108" spans="2:51" ht="26">
+    <row r="108" spans="2:51" ht="27">
       <c r="B108" s="74" t="s">
         <v>28</v>
       </c>
@@ -62977,7 +63213,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="109" spans="2:51" ht="131">
+    <row r="109" spans="2:51" ht="136.5">
       <c r="B109" s="73" t="s">
         <v>29</v>
       </c>
@@ -63021,7 +63257,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="110" spans="2:51" ht="39.5" thickBot="1">
+    <row r="110" spans="2:51" ht="41.25" thickBot="1">
       <c r="B110" s="75" t="s">
         <v>31</v>
       </c>
@@ -63067,7 +63303,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="111" spans="2:51" ht="13.5" thickTop="1">
+    <row r="111" spans="2:51" ht="14.25" thickTop="1">
       <c r="B111" s="76" t="s">
         <v>267</v>
       </c>
@@ -63297,7 +63533,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="116" spans="2:17" ht="13.5" thickBot="1">
+    <row r="116" spans="2:17" ht="14.25" thickBot="1">
       <c r="B116" s="22" t="s">
         <v>253</v>
       </c>
@@ -63435,14 +63671,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="88" t="s">
         <v>87</v>
       </c>
@@ -63452,7 +63688,7 @@
       </c>
       <c r="D2" s="89"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="82" t="s">
         <v>85</v>
       </c>
@@ -63463,7 +63699,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -63474,7 +63710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -63485,7 +63721,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -63496,7 +63732,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -63507,7 +63743,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -63529,7 +63765,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -63540,7 +63776,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -63551,7 +63787,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -63562,7 +63798,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -63573,7 +63809,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -63584,7 +63820,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -63606,7 +63842,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -63617,7 +63853,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -63628,7 +63864,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -63661,7 +63897,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="27">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -63672,7 +63908,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="26">
+    <row r="23" spans="2:4" ht="27">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -63698,7 +63934,7 @@
       <c r="C26" s="92"/>
       <c r="D26" s="78"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="93"/>
       <c r="D27" s="5"/>
